--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.34147</v>
+        <v>17.06525</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64838</v>
+        <v>16.92477</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82462</v>
+        <v>16.98898</v>
       </c>
       <c r="F2" t="n">
-        <v>42.64765</v>
+        <v>43.34432</v>
       </c>
       <c r="G2" t="n">
         <v>0.05153</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85341</v>
+        <v>1.88317</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.25534</v>
+        <v>17.19544</v>
       </c>
       <c r="D3" t="n">
-        <v>17.00806</v>
+        <v>16.73391</v>
       </c>
       <c r="E3" t="n">
-        <v>16.96638</v>
+        <v>17.00569</v>
       </c>
       <c r="F3" t="n">
-        <v>42.81063</v>
+        <v>43.53139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05225</v>
+        <v>0.05217</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85985</v>
+        <v>1.86392</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.92088</v>
+        <v>17.7295</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60769</v>
+        <v>16.44647</v>
       </c>
       <c r="E4" t="n">
-        <v>17.06772</v>
+        <v>16.90115</v>
       </c>
       <c r="F4" t="n">
-        <v>42.8936</v>
+        <v>43.51814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.051</v>
+        <v>0.05112</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84017</v>
+        <v>1.89824</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.16347</v>
+        <v>16.81758</v>
       </c>
       <c r="D6" t="n">
-        <v>16.02722</v>
+        <v>16.68725</v>
       </c>
       <c r="E6" t="n">
-        <v>16.59711</v>
+        <v>16.75826</v>
       </c>
       <c r="F6" t="n">
-        <v>22.41922</v>
+        <v>21.90619</v>
       </c>
       <c r="G6" t="n">
-        <v>34.9649</v>
+        <v>34.86945</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.14099</v>
+        <v>16.70799</v>
       </c>
       <c r="D7" t="n">
-        <v>16.38887</v>
+        <v>16.57133</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9895</v>
+        <v>16.67346</v>
       </c>
       <c r="F7" t="n">
-        <v>22.13249</v>
+        <v>22.54428</v>
       </c>
       <c r="G7" t="n">
-        <v>35.41431</v>
+        <v>35.08483</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83987</v>
+        <v>17.13243</v>
       </c>
       <c r="D8" t="n">
-        <v>16.27572</v>
+        <v>16.52114</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50877</v>
+        <v>16.58266</v>
       </c>
       <c r="F8" t="n">
-        <v>22.26245</v>
+        <v>22.09188</v>
       </c>
       <c r="G8" t="n">
-        <v>34.06901</v>
+        <v>34.86662</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.62086</v>
+        <v>0.62117</v>
       </c>
       <c r="D10" t="n">
-        <v>1.13266</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61791</v>
+        <v>0.61986</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12466</v>
+        <v>1.12498</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.62222</v>
+        <v>0.62085</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11743</v>
+        <v>1.12603</v>
       </c>
     </row>
   </sheetData>
